--- a/financial_advisor_forms/013_fia_suitability_assessment_form--financial_advisor_forms.xlsx
+++ b/financial_advisor_forms/013_fia_suitability_assessment_form--financial_advisor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What are the client's goals</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What are the client's primary financial goals?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please describe the client's main objectives.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -538,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>risk_tolerance</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is the client's risk tolerance?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please select the risk level that best describes the client.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -561,7 +569,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>time_horizon</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What is the client's time horizon for investment?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please select the time period for the investment.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -594,10 +606,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>risk_free_asset</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What type of assets do you currently have that are not invested?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please list the types of assets.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fixed_annuity</t>
+          <t>income_type</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fixed_annuity</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What is the client's income type?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please select the income type.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>tax_deficiency</t>
+          <t>financial_status</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tax_deficiency</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What is the client's financial status?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please select the financial status.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>risk_level</t>
+          <t>tax_deficiency</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>risk_level</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is the client's tax rate?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please select the tax rate.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -676,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>time_period</t>
+          <t>asset_allocation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>time_period</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What is the client's asset allocation?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please describe the asset allocation.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>asset_allocation</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>asset_allocation</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is the client's cash flow?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please select the cash flow.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -722,46 +758,54 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>investment_return</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What is the client's investment return expectation?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please describe the investment return expectation.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>tax_rate</t>
+          <t>investment_period</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>tax_rate</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is the client's investment period?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please select the investment period.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,317 +817,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fixed_annuity_type</t>
+          <t>asset_type</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>fixed_annuity_type</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What type of assets do you currently have invested?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please list the types of assets.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>income_type</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>income_type</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>asset_type</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>asset_type</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>investment_goals</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>investment_goals</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>risk_tolerance</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>risk_tolerance</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>financial_status</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>financial_status</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>tax_deficiency</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>tax_deficiency</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>tax_rate</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>tax_rate</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>asset_allocation</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>asset_allocation</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>investment_return</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>investment_return</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>investment_period</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>investment_period</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>asset_type</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>asset_type</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,459 +875,459 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>time_horizon_choices</t>
+          <t>risk_tolerance_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1._short-term</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1. Short-term</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>time_horizon_choices</t>
+          <t>risk_tolerance_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2._medium-term</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2. Medium-term</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>time_horizon_choices</t>
+          <t>risk_tolerance_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3._long-term</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3. Long-term</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>risk_free_asset_choices</t>
+          <t>time_horizon_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1._bonds</t>
+          <t>1-5_years</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1. Bonds</t>
+          <t>1-5 years</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>risk_free_asset_choices</t>
+          <t>time_horizon_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2._cds</t>
+          <t>5-10_years</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2. CDs</t>
+          <t>5-10 years</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>risk_free_asset_choices</t>
+          <t>time_horizon_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3._money_markets</t>
+          <t>10-20_years</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3. Money Markets</t>
+          <t>10-20 years</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fixed_annuity_choices</t>
+          <t>time_horizon_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1._high</t>
+          <t>20+_years</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1. High</t>
+          <t>20+ years</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fixed_annuity_choices</t>
+          <t>risk_free_asset_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2._medium</t>
+          <t>bonds</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2. Medium</t>
+          <t>Bonds</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fixed_annuity_choices</t>
+          <t>risk_free_asset_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3._low</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3. Low</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time_period_choices</t>
+          <t>risk_free_asset_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1._1-5_years</t>
+          <t>stocks</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1. 1-5 years</t>
+          <t>Stocks</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time_period_choices</t>
+          <t>risk_free_asset_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2._5-10_years</t>
+          <t>real_estate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2. 5-10 years</t>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>time_period_choices</t>
+          <t>income_type_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3._10-20_years</t>
+          <t>salary</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3. 10-20 years</t>
+          <t>Salary</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time_period_choices</t>
+          <t>income_type_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4._20+_years</t>
+          <t>self-employment</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4. 20+ years</t>
+          <t>Self-employment</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cash_flow_choices</t>
+          <t>income_type_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1._low</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1. Low</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cash_flow_choices</t>
+          <t>financial_status_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2._medium</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2. Medium</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cash_flow_choices</t>
+          <t>financial_status_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3._high</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3. High</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tax_rate_choices</t>
+          <t>financial_status_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1._high</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1. High</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tax_rate_choices</t>
+          <t>tax_deficiency_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2._medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2. Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tax_rate_choices</t>
+          <t>tax_deficiency_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3._low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3. Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fixed_annuity_type_choices</t>
+          <t>tax_deficiency_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1._fixed_income</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1. Fixed Income</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fixed_annuity_type_choices</t>
+          <t>cash_flow_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2._fixed</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2. Fixed</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fixed_annuity_type_choices</t>
+          <t>cash_flow_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3._variable</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3. Variable</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>income_type_choices</t>
+          <t>cash_flow_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1._salary</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1. Salary</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>income_type_choices</t>
+          <t>investment_period_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2._self-employment</t>
+          <t>1-5_years</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2. Self-employment</t>
+          <t>1-5 years</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>income_type_choices</t>
+          <t>investment_period_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3._business</t>
+          <t>5-10_years</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3. Business</t>
+          <t>5-10 years</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>asset_type_choices</t>
+          <t>investment_period_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1._cash</t>
+          <t>10-20_years</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1. Cash</t>
+          <t>10-20 years</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>asset_type_choices</t>
+          <t>investment_period_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2._bonds</t>
+          <t>20+_years</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2. Bonds</t>
+          <t>20+ years</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1339,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3._stocks</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3. Stocks</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1607,352 +1356,46 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4._real_estate</t>
+          <t>bonds</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4. Real Estate</t>
+          <t>Bonds</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>financial_status_choices</t>
+          <t>asset_type_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1._retired</t>
+          <t>stocks</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1. Retired</t>
+          <t>Stocks</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>financial_status_choices</t>
+          <t>asset_type_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2._inactive</t>
+          <t>real_estate</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2. Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>financial_status_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3._active</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>3. Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>tax_deficiency_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1._high</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1. High</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>tax_deficiency_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2._medium</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2. Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>tax_deficiency_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>3._low</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>3. Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>tax_rate_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1._high</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1. High</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>tax_rate_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2._medium</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2. Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>tax_rate_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>3._low</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>3. Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>cash_flow_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1._low</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1. Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>cash_flow_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2._medium</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2. Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>cash_flow_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>3._high</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>3. High</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>investment_period_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>1._1-5_years</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1. 1-5 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>investment_period_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2._5-10_years</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2. 5-10 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>investment_period_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>3._10-20_years</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>3. 10-20 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>investment_period_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>4._20+_years</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>4. 20+ years</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>asset_type_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1._cash</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1. Cash</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>asset_type_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2._bonds</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2. Bonds</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>asset_type_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>3._stocks</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>3. Stocks</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>asset_type_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>4._real_estate</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>4. Real Estate</t>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
